--- a/assets/csv/alumni.xlsx
+++ b/assets/csv/alumni.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/hassan_491_osu_edu/Documents/Documents/GitHub/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692F5132-72D2-3E48-819B-3859C734EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{692F5132-72D2-3E48-819B-3859C734EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4B173C8-238B-C14B-B341-11FF505C7AF9}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="127">
   <si>
     <t>Sl.</t>
   </si>
@@ -161,9 +161,6 @@
     <t>Kaareen</t>
   </si>
   <si>
-    <t>Mahbub</t>
-  </si>
-  <si>
     <t xml:space="preserve">Md Muntasir </t>
   </si>
   <si>
@@ -194,9 +191,6 @@
     <t xml:space="preserve">Rubel </t>
   </si>
   <si>
-    <t>Yousuf</t>
-  </si>
-  <si>
     <t>Zia Ul</t>
   </si>
   <si>
@@ -281,9 +275,6 @@
     <t xml:space="preserve"> Aadeeba </t>
   </si>
   <si>
-    <t xml:space="preserve">Ayeman </t>
-  </si>
-  <si>
     <t>Zitu</t>
   </si>
   <si>
@@ -305,9 +296,6 @@
     <t>Islam</t>
   </si>
   <si>
-    <t>Ali Raju</t>
-  </si>
-  <si>
     <t>Haq</t>
   </si>
   <si>
@@ -351,6 +339,84 @@
   </si>
   <si>
     <t>Mechanical and Aerospace Engineering</t>
+  </si>
+  <si>
+    <t>Mohammad Mahafuzur</t>
+  </si>
+  <si>
+    <t>Rahaman</t>
+  </si>
+  <si>
+    <t>Materials Science and Engineering</t>
+  </si>
+  <si>
+    <t>Rokaiya</t>
+  </si>
+  <si>
+    <t>Shatadru</t>
+  </si>
+  <si>
+    <t>Microbiology</t>
+  </si>
+  <si>
+    <t>Saqeeb</t>
+  </si>
+  <si>
+    <t>Shamma Jabeen</t>
+  </si>
+  <si>
+    <t>Proma</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>Md Washim</t>
+  </si>
+  <si>
+    <t>Akram</t>
+  </si>
+  <si>
+    <t>Food, Agricultural and Biological Engineering</t>
+  </si>
+  <si>
+    <t>Md Minhazul</t>
+  </si>
+  <si>
+    <t>Ahmad Ilderim</t>
+  </si>
+  <si>
+    <t>Tokey</t>
+  </si>
+  <si>
+    <t>Geography</t>
+  </si>
+  <si>
+    <t>Taosif</t>
+  </si>
+  <si>
+    <t>Biostatistics</t>
+  </si>
+  <si>
+    <t>Civil Engineering</t>
+  </si>
+  <si>
+    <t>Law</t>
+  </si>
+  <si>
+    <t>Molecular, Cellular, and Developmental Biology</t>
+  </si>
+  <si>
+    <t>School of Environment and Natural Resources</t>
+  </si>
+  <si>
+    <t>Biomedical Informatics</t>
+  </si>
+  <si>
+    <t>Pharmacoepidemiology</t>
+  </si>
+  <si>
+    <t>Biochemistry</t>
   </si>
 </sst>
 </file>
@@ -462,7 +528,87 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -803,9 +949,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1650962B-F96C-FE4E-A26E-251242D6E0F9}">
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="5" max="5" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -835,13 +982,15 @@
         <v>12</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
@@ -849,14 +998,14 @@
         <v>13</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -865,13 +1014,15 @@
         <v>14</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F4" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
@@ -879,14 +1030,14 @@
         <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -895,11 +1046,15 @@
         <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
@@ -907,14 +1062,14 @@
         <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -923,14 +1078,14 @@
         <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -939,14 +1094,14 @@
         <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -959,9 +1114,11 @@
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
@@ -969,13 +1126,15 @@
         <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
@@ -983,13 +1142,15 @@
         <v>21</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
@@ -997,14 +1158,14 @@
         <v>22</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -1013,11 +1174,15 @@
         <v>23</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
@@ -1025,13 +1190,15 @@
         <v>24</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
@@ -1043,9 +1210,11 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
@@ -1053,11 +1222,11 @@
         <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1067,14 +1236,14 @@
         <v>26</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -1083,14 +1252,14 @@
         <v>27</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -1099,13 +1268,15 @@
         <v>28</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
@@ -1113,13 +1284,15 @@
         <v>29</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
@@ -1127,14 +1300,14 @@
         <v>30</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1143,14 +1316,14 @@
         <v>31</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1159,13 +1332,15 @@
         <v>32</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
@@ -1173,14 +1348,14 @@
         <v>33</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1189,13 +1364,15 @@
         <v>34</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
@@ -1203,14 +1380,14 @@
         <v>35</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1219,13 +1396,15 @@
         <v>36</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
@@ -1233,11 +1412,11 @@
         <v>37</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F29" s="4"/>
     </row>
@@ -1247,13 +1426,15 @@
         <v>38</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
@@ -1265,7 +1446,7 @@
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F31" s="4"/>
     </row>
@@ -1275,11 +1456,11 @@
         <v>40</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F32" s="4"/>
     </row>
@@ -1289,13 +1470,15 @@
         <v>41</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F33" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3"/>
@@ -1303,13 +1486,15 @@
         <v>42</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F34" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="3"/>
@@ -1317,13 +1502,15 @@
         <v>43</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F35" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
@@ -1331,39 +1518,45 @@
         <v>44</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F36" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3"/>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
@@ -1371,14 +1564,14 @@
         <v>47</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -1387,13 +1580,15 @@
         <v>48</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F40" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
@@ -1401,10 +1596,15 @@
         <v>49</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="F41" s="10"/>
+      <c r="E41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
@@ -1412,13 +1612,15 @@
         <v>50</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
@@ -1426,107 +1628,157 @@
         <v>51</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="F43" s="6"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>89</v>
+      <c r="C44" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="D44" s="4"/>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F44" s="6"/>
+      <c r="F44" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
-      <c r="B45" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>90</v>
+      <c r="B45" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="D45" s="4"/>
-      <c r="E45" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F45" s="6"/>
+      <c r="E45" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>103</v>
+        <v>89</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
+      <c r="B47" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="6"/>
+      <c r="E47" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="11"/>
+      <c r="E48" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
+      <c r="B49" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
+      <c r="E49" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
+      <c r="E50" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="3"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
+      <c r="B51" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
+      <c r="E51" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="3"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="3"/>
@@ -1794,38 +2046,46 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="3"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="3"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" s="3"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="3"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="B53:B1048576 B1:B44">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/csv/alumni.xlsx
+++ b/assets/csv/alumni.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/hassan_491_osu_edu/Documents/Documents/GitHub/bgsa-osu.github.io/assets/csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kmnaimulhassan/Documents/GitHub-imac/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{692F5132-72D2-3E48-819B-3859C734EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4B173C8-238B-C14B-B341-11FF505C7AF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B702FD6-9603-1849-BFAF-08352F3392FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
+    <workbookView xWindow="49340" yWindow="8940" windowWidth="29400" windowHeight="18460" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="129">
   <si>
     <t>Sl.</t>
   </si>
@@ -417,6 +417,12 @@
   </si>
   <si>
     <t>Biochemistry</t>
+  </si>
+  <si>
+    <t>Md Sakib</t>
+  </si>
+  <si>
+    <t>Anwar</t>
   </si>
 </sst>
 </file>
@@ -528,7 +534,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1782,11 +1798,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="3"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
+      <c r="B53" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+      <c r="E53" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
@@ -2061,31 +2085,34 @@
       <c r="F87" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B53:B1048576 B1:B44">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54:B1048576 B1:B44">
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
